--- a/data/trans_orig/P43A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43A-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>38731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>63435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>38731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>63435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70529</t>
+          <t>70711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99628</t>
+          <t>99726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70529</t>
+          <t>70711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99628</t>
+          <t>99726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>67163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>67163</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>42189</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68518</t>
+          <t>67636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>42189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68518</t>
+          <t>67636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67085</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98617</t>
+          <t>99568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67085</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98617</t>
+          <t>99568</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101053</t>
+          <t>101174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135323</t>
+          <t>137678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101053</t>
+          <t>101174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135323</t>
+          <t>137678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>64804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97407</t>
+          <t>96439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>64804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97407</t>
+          <t>96439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>47337</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74734</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>47337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74734</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59074</t>
+          <t>59984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89718</t>
+          <t>89424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59074</t>
+          <t>59984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89718</t>
+          <t>89424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75166</t>
+          <t>73337</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105021</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75166</t>
+          <t>73337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>105021</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81821</t>
+          <t>82499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81821</t>
+          <t>82499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22119</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22119</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>82890</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>117650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>82890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>117650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136783</t>
+          <t>136333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174374</t>
+          <t>176229</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136783</t>
+          <t>136333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174374</t>
+          <t>176229</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76763</t>
+          <t>78565</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>110244</t>
+          <t>111940</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76763</t>
+          <t>78565</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110244</t>
+          <t>111940</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58997</t>
+          <t>59086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90201</t>
+          <t>91633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58997</t>
+          <t>59086</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90201</t>
+          <t>91633</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87723</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87723</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94250</t>
+          <t>93340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130944</t>
+          <t>127717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94250</t>
+          <t>93340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130944</t>
+          <t>127717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -2970,12 +2970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81096</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112562</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81096</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112562</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36779</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63975</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36779</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63975</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>58979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91469</t>
+          <t>90058</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>58979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91469</t>
+          <t>90058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174026</t>
+          <t>174406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>218186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174026</t>
+          <t>174406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>218186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105124</t>
+          <t>103505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145081</t>
+          <t>143760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105124</t>
+          <t>103505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145081</t>
+          <t>143760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86167</t>
+          <t>85736</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86167</t>
+          <t>85736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>51775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>51775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>125516</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167823</t>
+          <t>167223</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>125516</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>167823</t>
+          <t>167223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -3758,12 +3758,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80686</t>
+          <t>80246</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114883</t>
+          <t>119253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80686</t>
+          <t>80246</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114883</t>
+          <t>119253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43927</t>
+          <t>44798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>76607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43927</t>
+          <t>44798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>76607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -3996,12 +3996,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111346</t>
+          <t>109044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151081</t>
+          <t>149868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111346</t>
+          <t>109044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151081</t>
+          <t>149868</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163327</t>
+          <t>162176</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205870</t>
+          <t>205679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>163327</t>
+          <t>162176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205870</t>
+          <t>205679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -4152,12 +4152,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>105700</t>
+          <t>105874</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>145524</t>
+          <t>146599</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105700</t>
+          <t>105874</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145524</t>
+          <t>146599</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81496</t>
+          <t>80935</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81496</t>
+          <t>80935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>308016</t>
+          <t>309091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>378446</t>
+          <t>377771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>308016</t>
+          <t>309091</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>378446</t>
+          <t>377771</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>597342</t>
+          <t>598796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>677877</t>
+          <t>677245</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>597342</t>
+          <t>598796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>677877</t>
+          <t>677245</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>403737</t>
+          <t>406435</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>477365</t>
+          <t>480577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>403737</t>
+          <t>406435</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>477365</t>
+          <t>480577</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>212358</t>
+          <t>213239</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>274247</t>
+          <t>272911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>212358</t>
+          <t>213239</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>274247</t>
+          <t>272911</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84529</t>
+          <t>83849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117092</t>
+          <t>119563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84529</t>
+          <t>83849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117092</t>
+          <t>119563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -5033,12 +5033,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103090</t>
+          <t>105194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138804</t>
+          <t>138299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103090</t>
+          <t>105194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138804</t>
+          <t>138299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81396</t>
+          <t>83613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81396</t>
+          <t>83613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>33585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58533</t>
+          <t>58687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>33585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58533</t>
+          <t>58687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5349,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98903</t>
+          <t>98804</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>141165</t>
+          <t>139516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98903</t>
+          <t>98804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>141165</t>
+          <t>139516</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>204998</t>
+          <t>204859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253532</t>
+          <t>253722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204998</t>
+          <t>204859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253532</t>
+          <t>253722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122434</t>
+          <t>122839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165255</t>
+          <t>164394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122434</t>
+          <t>122839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165255</t>
+          <t>164394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -5583,12 +5583,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68977</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68977</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>57026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88109</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>57026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88109</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -5821,12 +5821,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138401</t>
+          <t>138070</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>175594</t>
+          <t>179138</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138401</t>
+          <t>138070</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>175594</t>
+          <t>179138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90793</t>
+          <t>91186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90793</t>
+          <t>91186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -5977,12 +5977,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28940</t>
+          <t>27988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51761</t>
+          <t>53444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28940</t>
+          <t>27988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51761</t>
+          <t>53444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -6137,12 +6137,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117832</t>
+          <t>117949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>161171</t>
+          <t>162094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117832</t>
+          <t>117949</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161171</t>
+          <t>162094</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6187,12 +6187,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176156</t>
+          <t>174832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223945</t>
+          <t>223177</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>176156</t>
+          <t>174832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223945</t>
+          <t>223177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6265,12 +6265,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>106643</t>
+          <t>107776</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>148506</t>
+          <t>149533</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>106643</t>
+          <t>107776</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148506</t>
+          <t>149533</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6343,12 +6343,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55799</t>
+          <t>55778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90815</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55799</t>
+          <t>55778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90815</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -6531,12 +6531,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>393266</t>
+          <t>388794</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>465610</t>
+          <t>467388</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>393266</t>
+          <t>388794</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>465610</t>
+          <t>467388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6581,12 +6581,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -6609,12 +6609,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>658788</t>
+          <t>664508</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>746128</t>
+          <t>747576</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>658788</t>
+          <t>664508</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>746128</t>
+          <t>747576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>378201</t>
+          <t>376572</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>450296</t>
+          <t>450291</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>378201</t>
+          <t>376572</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>450296</t>
+          <t>450291</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184251</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>237087</t>
+          <t>239535</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184251</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>237087</t>
+          <t>239535</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -7091,32 +7091,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100066</t>
+          <t>105319</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89032</t>
+          <t>93979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110736</t>
+          <t>117119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7126,32 +7126,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100066</t>
+          <t>105319</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89032</t>
+          <t>93979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110736</t>
+          <t>117119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -7169,32 +7169,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>88150</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>77223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90989</t>
+          <t>99707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7204,32 +7204,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>88150</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>77223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90989</t>
+          <t>99707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -7247,32 +7247,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64253</t>
+          <t>68004</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>58381</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74900</t>
+          <t>78557</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7282,32 +7282,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64253</t>
+          <t>68004</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>58381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74900</t>
+          <t>78557</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -7325,32 +7325,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>24951</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32290</t>
+          <t>33296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7360,32 +7360,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>24951</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32290</t>
+          <t>33296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -7403,17 +7403,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>268520</t>
+          <t>286424</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268520</t>
+          <t>286424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268520</t>
+          <t>286424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>268520</t>
+          <t>286424</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>268520</t>
+          <t>286424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268520</t>
+          <t>286424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7485,32 +7485,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112238</t>
+          <t>122243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97912</t>
+          <t>109224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126182</t>
+          <t>137040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7520,32 +7520,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>112238</t>
+          <t>122243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97912</t>
+          <t>109224</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126182</t>
+          <t>137040</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -7563,32 +7563,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>121511</t>
+          <t>135304</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108156</t>
+          <t>121521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134855</t>
+          <t>150556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>121511</t>
+          <t>135304</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108156</t>
+          <t>121521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134855</t>
+          <t>150556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -7641,32 +7641,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82975</t>
+          <t>93890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71116</t>
+          <t>81263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95627</t>
+          <t>107941</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7676,32 +7676,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82975</t>
+          <t>93890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71116</t>
+          <t>81263</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95627</t>
+          <t>107941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -7719,32 +7719,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>49209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35666</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>60833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7754,32 +7754,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>49209</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35666</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>60833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -7797,17 +7797,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>361720</t>
+          <t>400646</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>361720</t>
+          <t>400646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>361720</t>
+          <t>400646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7832,17 +7832,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>361720</t>
+          <t>400646</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>361720</t>
+          <t>400646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361720</t>
+          <t>400646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7879,32 +7879,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>115099</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>76947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215364</t>
+          <t>102721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7914,32 +7914,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>115099</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>76947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215364</t>
+          <t>102721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -7957,32 +7957,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>295249</t>
+          <t>102084</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>137424</t>
+          <t>88334</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>425059</t>
+          <t>116521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7992,32 +7992,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>295249</t>
+          <t>102084</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>137424</t>
+          <t>88334</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>425059</t>
+          <t>116521</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -8035,32 +8035,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>61582</t>
+          <t>68672</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>57873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>82717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61582</t>
+          <t>68672</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>57873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>82717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -8113,32 +8113,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8148,32 +8148,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -8191,17 +8191,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>505005</t>
+          <t>296908</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>505005</t>
+          <t>296908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>505005</t>
+          <t>296908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8226,17 +8226,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>505005</t>
+          <t>296908</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>505005</t>
+          <t>296908</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>505005</t>
+          <t>296908</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>154285</t>
+          <t>164299</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138302</t>
+          <t>148736</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>168487</t>
+          <t>181870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8308,32 +8308,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>154285</t>
+          <t>164299</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>138302</t>
+          <t>148736</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>168487</t>
+          <t>181870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8351,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>123888</t>
+          <t>132244</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109834</t>
+          <t>117092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140737</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8386,32 +8386,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>123888</t>
+          <t>132244</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109834</t>
+          <t>117092</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140737</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -8429,32 +8429,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>100889</t>
+          <t>110645</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87352</t>
+          <t>94886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>115726</t>
+          <t>125837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8464,32 +8464,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100889</t>
+          <t>110645</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87352</t>
+          <t>94886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115726</t>
+          <t>125837</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -8507,32 +8507,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64141</t>
+          <t>70001</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52516</t>
+          <t>57338</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77610</t>
+          <t>83396</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8542,32 +8542,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>64141</t>
+          <t>70001</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52516</t>
+          <t>57338</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77610</t>
+          <t>83396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -8585,17 +8585,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>443204</t>
+          <t>477189</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>443204</t>
+          <t>477189</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>443204</t>
+          <t>477189</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8620,17 +8620,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>443204</t>
+          <t>477189</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>443204</t>
+          <t>477189</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>443204</t>
+          <t>477189</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8667,32 +8667,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>481689</t>
+          <t>482169</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>322657</t>
+          <t>451440</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>574275</t>
+          <t>509621</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8702,32 +8702,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>481689</t>
+          <t>482169</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>322657</t>
+          <t>451440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>574275</t>
+          <t>509621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>466801</t>
+          <t>431618</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>956590</t>
+          <t>487799</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>466801</t>
+          <t>431618</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>956590</t>
+          <t>487799</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -8823,32 +8823,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>309699</t>
+          <t>341211</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>313123</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>364691</t>
+          <t>367224</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8858,32 +8858,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>309699</t>
+          <t>341211</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>313123</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>364691</t>
+          <t>367224</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -8901,32 +8901,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>109433</t>
+          <t>162379</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>199522</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8936,32 +8936,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>109433</t>
+          <t>162379</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>199522</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -8979,17 +8979,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9014,17 +9014,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
